--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Unadjusted_Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Unadjusted_Boot.xlsx
@@ -377,10 +377,10 @@
         <v>27.469</v>
       </c>
       <c r="B2">
-        <v>27.157</v>
+        <v>27.153</v>
       </c>
       <c r="C2">
-        <v>27.783</v>
+        <v>27.786</v>
       </c>
     </row>
   </sheetData>
@@ -418,7 +418,7 @@
         <v>27.595</v>
       </c>
       <c r="C2">
-        <v>28.233</v>
+        <v>28.212</v>
       </c>
     </row>
   </sheetData>
